--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED09.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED09.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>195W</t>
+          <t>116W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N3"/>
+  <dimension ref="B2:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -917,6 +917,18 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>贷款时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2季</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>99W</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L5"/>
+  <dimension ref="B2:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1712,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0095</t>
+          <t>SIM_XA_FIXED-4-0021</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1726,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49W</t>
+          <t>99W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,17 +1740,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第2年</t>
+          <t>第4年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,62 +1760,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第2年4季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-3-0084</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>140W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第3年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第4年2季</t>
+          <t>第5年2季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G55"/>
+  <dimension ref="B2:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2189,14 +2146,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Auction_Win</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2162,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
         </is>
       </c>
     </row>
@@ -2215,14 +2172,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2231,7 +2188,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-c77b15aca6", "line_id": "L-9a3ddca748", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2248,11 +2205,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2274,11 +2231,11 @@
         <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2293,14 +2250,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>-15</v>
       </c>
       <c r="E20" t="n">
-        <v>455</v>
+        <v>407</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2266,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0095", "receivable_term_quarters": 0, "revenue_wan": 49.0}</t>
+          <t>maintenance_expense | {"line_id": "L-9a3ddca748"}</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2276,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2335,7 +2292,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-9a3ddca748", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2345,14 +2302,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2361,7 +2318,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-36695c7dc2", "line_id": "L-9a3ddca748", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2371,23 +2328,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E23" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2397,23 +2354,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-9a3ddca748"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2380,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-9a3ddca748", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2406,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2475,23 +2432,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2501,23 +2458,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E28" t="n">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-9a3ddca748"}</t>
         </is>
       </c>
     </row>
@@ -2527,23 +2484,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-9a3ddca748", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2510,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2579,23 +2536,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="E31" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2605,23 +2562,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-32b656e4b4", "line_id": "L-9a3ddca748", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2595,11 @@
         <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2657,23 +2614,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-9a3ddca748"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2683,23 +2640,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="E35" t="n">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-9a3ddca748", "asset_type": "factory"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2666,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="E36" t="n">
-        <v>271</v>
+        <v>206</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-7da56dc3c3", "line_id": "L-9a3ddca748", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2692,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>267</v>
+        <v>192</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2718,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E38" t="n">
-        <v>253</v>
+        <v>177</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-9a3ddca748"}</t>
         </is>
       </c>
     </row>
@@ -2787,23 +2744,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>253</v>
+        <v>177</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0084", "receivable_term_quarters": 3, "revenue_wan": 140.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-9a3ddca748", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2813,23 +2770,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2839,23 +2796,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="E41" t="n">
         <v>173</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-3df70cb8cf", "line_id": "L-9a3ddca748", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2833,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2891,23 +2848,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0021", "receivable_term_quarters": 4, "revenue_wan": 99.0}</t>
         </is>
       </c>
     </row>
@@ -2924,11 +2881,11 @@
         <v>-14</v>
       </c>
       <c r="E44" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2943,23 +2900,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>140</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>271</v>
+        <v>131</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-295423ca7c"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2976,11 +2933,11 @@
         <v>-15</v>
       </c>
       <c r="E46" t="n">
-        <v>256</v>
+        <v>116</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3002,11 +2959,11 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>256</v>
+        <v>116</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3028,196 +2985,14 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>256</v>
+        <v>116</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>46</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Pay_AD</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E49" t="n">
-        <v>252</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="n">
-        <v>47</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E50" t="n">
-        <v>238</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E51" t="n">
-        <v>224</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E52" t="n">
-        <v>210</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E53" t="n">
-        <v>195</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-9a3ddca748"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>195</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-9a3ddca748", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>195</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-9a3ddca748", "asset_type": "production_line"}</t>
         </is>
@@ -3611,16 +3386,16 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -3636,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>80</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3661,16 +3436,16 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -3711,16 +3486,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-66</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
         <v>-75</v>
       </c>
       <c r="G20" t="n">
-        <v>-15</v>
+        <v>-75</v>
       </c>
       <c r="H20" t="n">
-        <v>-61</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="21">
@@ -3761,16 +3536,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-81.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
         <v>-90.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.2</v>
+        <v>-57.2</v>
       </c>
     </row>
     <row r="23">
@@ -3811,16 +3586,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-81.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F24" t="n">
         <v>-90.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-76.2</v>
+        <v>-57.2</v>
       </c>
     </row>
     <row r="25">
@@ -3861,16 +3636,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-81.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F26" t="n">
         <v>-90.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-30.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-76.2</v>
+        <v>-57.2</v>
       </c>
     </row>
     <row r="28">
@@ -3960,16 +3735,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="F30" t="n">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="G30" t="n">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="H30" t="n">
-        <v>195</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31">
@@ -3994,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
@@ -4010,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4038,13 +3813,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4085,16 +3860,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="F35" t="n">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="G35" t="n">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="H35" t="n">
-        <v>275</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36">
@@ -4210,16 +3985,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>507.6</v>
+        <v>488.6</v>
       </c>
       <c r="F40" t="n">
-        <v>417.4</v>
+        <v>398.4</v>
       </c>
       <c r="G40" t="n">
-        <v>387.2</v>
+        <v>308.2</v>
       </c>
       <c r="H40" t="n">
-        <v>311</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41">
@@ -4385,16 +4160,16 @@
         <v>-4.263256414560601e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>-86.20000000000009</v>
+        <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-167.4000000000001</v>
+        <v>-186.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-257.6000000000001</v>
+        <v>-276.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-287.8000000000001</v>
+        <v>-366.8</v>
       </c>
     </row>
     <row r="48">
@@ -4410,16 +4185,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-81.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F48" t="n">
         <v>-90.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-30.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-76.2</v>
+        <v>-57.2</v>
       </c>
     </row>
     <row r="49">
@@ -4435,16 +4210,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>507.5999999999999</v>
+        <v>488.6</v>
       </c>
       <c r="F49" t="n">
-        <v>417.3999999999999</v>
+        <v>398.4</v>
       </c>
       <c r="G49" t="n">
-        <v>387.1999999999999</v>
+        <v>308.2</v>
       </c>
       <c r="H49" t="n">
-        <v>310.9999999999999</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50">
@@ -4460,16 +4235,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>507.5999999999999</v>
+        <v>488.6</v>
       </c>
       <c r="F50" t="n">
-        <v>417.3999999999999</v>
+        <v>398.4</v>
       </c>
       <c r="G50" t="n">
-        <v>387.1999999999999</v>
+        <v>308.2</v>
       </c>
       <c r="H50" t="n">
-        <v>310.9999999999999</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
